--- a/data/trans_orig/P21D_6_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D_6_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>670</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>256911</t>
+          <t>256891</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>293129</t>
+          <t>293379</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>298535</t>
+          <t>298459</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>552733</t>
+          <t>554626</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>564446</t>
+          <t>564517</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>9158</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7414</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13155</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>649377</t>
+          <t>648452</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>439276</t>
+          <t>439358</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>445246</t>
+          <t>445345</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1091227</t>
+          <t>1091548</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1102330</t>
+          <t>1102166</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>322282</t>
+          <t>323497</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>321782</t>
+          <t>322054</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327760</t>
+          <t>327615</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>648593</t>
+          <t>648715</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>656509</t>
+          <t>656648</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19827</t>
+          <t>19105</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>7968</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21983</t>
+          <t>22060</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>400027</t>
+          <t>400227</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>407390</t>
+          <t>407384</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>498115</t>
+          <t>498837</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>511759</t>
+          <t>512331</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>903912</t>
+          <t>903835</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>917715</t>
+          <t>917927</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>17563</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>13469</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29039</t>
+          <t>29134</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19536</t>
+          <t>19316</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40407</t>
+          <t>39603</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1644000</t>
+          <t>1644406</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1658617</t>
+          <t>1658234</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1563628</t>
+          <t>1563533</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1579275</t>
+          <t>1579198</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3214229</t>
+          <t>3215033</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3235100</t>
+          <t>3235320</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D_6_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D_6_R-Habitat-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9708</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11101</t>
+          <t>12368</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>264843</t>
+          <t>286255</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>256891</t>
+          <t>278599</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>296863</t>
+          <t>321143</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>293379</t>
+          <t>317554</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>298459</t>
+          <t>322845</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>561705</t>
+          <t>607398</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>554626</t>
+          <t>599264</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>564517</t>
+          <t>610249</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,67 +1103,67 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7414</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>6447</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>3096</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>12280</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>5975</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>2216</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>12834</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>655334</t>
+          <t>467017</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>648452</t>
+          <t>462168</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>657610</t>
+          <t>469205</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,67 +1216,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>443073</t>
+          <t>498543</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>439358</t>
+          <t>494127</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>445345</t>
+          <t>500926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>965560</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>959727</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>968911</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>98,74%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>99,68%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1120</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1098407</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1091548</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1102166</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>657610</t>
+          <t>469205</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>657610</t>
+          <t>469205</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>657610</t>
+          <t>469205</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>446772</t>
+          <t>502802</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>446772</t>
+          <t>502802</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>446772</t>
+          <t>502802</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1104382</t>
+          <t>972007</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1104382</t>
+          <t>972007</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1104382</t>
+          <t>972007</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>10607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>327927</t>
+          <t>373660</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>323497</t>
+          <t>368960</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>329808</t>
+          <t>375580</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>325810</t>
+          <t>374916</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>322054</t>
+          <t>371523</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327615</t>
+          <t>376960</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>653737</t>
+          <t>748575</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>648715</t>
+          <t>743026</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>656648</t>
+          <t>751274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>329808</t>
+          <t>375580</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>329808</t>
+          <t>375580</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>329808</t>
+          <t>375580</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>658632</t>
+          <t>753633</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>658632</t>
+          <t>753633</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>658632</t>
+          <t>753633</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>576</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7832</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10942</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19105</t>
+          <t>17805</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13627</t>
+          <t>13822</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7968</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22060</t>
+          <t>22319</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>405268</t>
+          <t>430704</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>400227</t>
+          <t>425527</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>407384</t>
+          <t>432783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>507000</t>
+          <t>479567</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>498837</t>
+          <t>472929</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>512331</t>
+          <t>484142</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>912268</t>
+          <t>910271</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>903835</t>
+          <t>901774</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>917927</t>
+          <t>915262</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17563</t>
+          <t>17198</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>14057</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29134</t>
+          <t>29193</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>29560</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19316</t>
+          <t>21586</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39603</t>
+          <t>40987</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1653372</t>
+          <t>1557637</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1644406</t>
+          <t>1549070</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1658234</t>
+          <t>1562333</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1572746</t>
+          <t>1674169</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1563533</t>
+          <t>1665905</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1579198</t>
+          <t>1681041</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3226118</t>
+          <t>3231805</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3215033</t>
+          <t>3220378</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3235320</t>
+          <t>3239779</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1661969</t>
+          <t>1566268</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1661969</t>
+          <t>1566268</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1661969</t>
+          <t>1566268</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1592667</t>
+          <t>1695098</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1592667</t>
+          <t>1695098</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1592667</t>
+          <t>1695098</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3254636</t>
+          <t>3261365</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3254636</t>
+          <t>3261365</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3254636</t>
+          <t>3261365</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
